--- a/tests/fixtures/products.xlsx
+++ b/tests/fixtures/products.xlsx
@@ -13,7 +13,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>商品名称</t>
+          <t>物料名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -33,12 +33,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>采购价</t>
+          <t>参考采购价</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>销售价</t>
+          <t>参考销售价</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
